--- a/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="1105">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>006</t>
   </si>
   <si>
-    <t>Andrologie</t>
+    <t>Andrologie (urologie médicale)</t>
   </si>
   <si>
     <t>007</t>
@@ -744,7 +744,7 @@
     <t>152</t>
   </si>
   <si>
-    <t>Urgences spécialisées Médico-Judiciaires (UMJ)</t>
+    <t>Evaluation Médico-Judiciaire (UMJ)</t>
   </si>
   <si>
     <t>154</t>
@@ -768,7 +768,7 @@
     <t>158</t>
   </si>
   <si>
-    <t>Urgences spécialisées psychiatriques</t>
+    <t>Urgences psychiatriques</t>
   </si>
   <si>
     <t>159</t>
@@ -1608,7 +1608,7 @@
     <t>309</t>
   </si>
   <si>
-    <t>Accompagnements à la vie affective et sexuelle</t>
+    <t>Accompagnements à la vie intime, affective et sexuelle</t>
   </si>
   <si>
     <t>310</t>
@@ -2370,7 +2370,7 @@
     <t>448</t>
   </si>
   <si>
-    <t>Diagnostic lié à un retard ou trouble du développement</t>
+    <t>Diagnostic lié à un retard ou Trouble du Neuro-Développement (TND)</t>
   </si>
   <si>
     <t>449</t>
@@ -2682,7 +2682,7 @@
     <t>510</t>
   </si>
   <si>
-    <t>Échographie obstétricale</t>
+    <t>Échographie obstétricale de dépistage (1er, 2ème, 3ème trimestre)</t>
   </si>
   <si>
     <t>511</t>
@@ -3225,10 +3225,100 @@
     <t>Médiation pour le maintien en hospitalisation</t>
   </si>
   <si>
+    <t>602</t>
+  </si>
+  <si>
+    <t>Pair aidance pour l'autodétermination</t>
+  </si>
+  <si>
     <t>603</t>
   </si>
   <si>
     <t>Prise en charge coordonnée des patients atteints de maladies neurodégénératives</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Chirurgie pédiatrique spécialisée orthopédique</t>
+  </si>
+  <si>
+    <t>605</t>
+  </si>
+  <si>
+    <t>Chirurgie pédiatrique spécialisée digestif et viscérale</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>Accompagnement pour l’autodétermination de la personne</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès des acteurs du secteur sanitaire</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès des acteurs du milieu ordinaire</t>
+  </si>
+  <si>
+    <t>609</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès de acteurs du secteur judiciaire</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>Pédiatrie spécialisée neurologie</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
+    <t>Pédiatrie spécialisée pneumologie</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>Psychiatrie de crise</t>
+  </si>
+  <si>
+    <t>613</t>
+  </si>
+  <si>
+    <t>Echographie obstétricale de diagnostic</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en pathologies chroniques stabilisées</t>
+  </si>
+  <si>
+    <t>615</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en oncologie et hémato-oncologie</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en maladie rénale chronique</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en santé mentale</t>
   </si>
   <si>
     <t/>
@@ -3499,7 +3589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7695,15 +7785,135 @@
         <v>1072</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="s" s="2">
+        <v>1076</v>
+      </c>
+      <c r="B526" t="s" s="2">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="s" s="2">
+        <v>1078</v>
+      </c>
+      <c r="B527" t="s" s="2">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="B528" t="s" s="2">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="s" s="2">
+        <v>1082</v>
+      </c>
+      <c r="B529" t="s" s="2">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="s" s="2">
+        <v>1084</v>
+      </c>
+      <c r="B530" t="s" s="2">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="s" s="2">
+        <v>1086</v>
+      </c>
+      <c r="B531" t="s" s="2">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="s" s="2">
+        <v>1088</v>
+      </c>
+      <c r="B532" t="s" s="2">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="s" s="2">
+        <v>1090</v>
+      </c>
+      <c r="B533" t="s" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="s" s="2">
+        <v>1092</v>
+      </c>
+      <c r="B534" t="s" s="2">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="s" s="2">
+        <v>1094</v>
+      </c>
+      <c r="B535" t="s" s="2">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="s" s="2">
+        <v>1096</v>
+      </c>
+      <c r="B536" t="s" s="2">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="B537" t="s" s="2">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="B538" t="s" s="2">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="s" s="2">
+        <v>1102</v>
+      </c>
+      <c r="B539" t="s" s="2">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="s" s="2">
+        <v>1103</v>
+      </c>
+      <c r="B540" t="s" s="2">
+        <v>1104</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -762,13 +762,13 @@
     <t>157</t>
   </si>
   <si>
-    <t>Urgences polyvalentes</t>
+    <t>Urgences polyvalentes hospitalières</t>
   </si>
   <si>
     <t>158</t>
   </si>
   <si>
-    <t>Urgences psychiatriques</t>
+    <t>Urgences psychiatriques hospitalières</t>
   </si>
   <si>
     <t>159</t>
@@ -972,7 +972,7 @@
     <t>201</t>
   </si>
   <si>
-    <t>Pédicure-Podologie</t>
+    <t>Pédicurie-Podologie (bilan diagnostic et mise en œuvre des activités thérapeutiques si nécessaire)</t>
   </si>
   <si>
     <t>202</t>
@@ -1254,7 +1254,7 @@
     <t>249</t>
   </si>
   <si>
-    <t>Urgences pédiatriques</t>
+    <t>Urgences pédiatriques hospitalières</t>
   </si>
   <si>
     <t>250</t>

--- a/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1127">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -735,12 +735,6 @@
     <t>Urgences Médico-Psychologiques (CUMP)</t>
   </si>
   <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>Urgences spécialisées cardiologiques</t>
-  </si>
-  <si>
     <t>152</t>
   </si>
   <si>
@@ -1728,7 +1722,7 @@
     <t>334</t>
   </si>
   <si>
-    <t>Activité de prévention</t>
+    <t>Activité de dépistage et de prévention</t>
   </si>
   <si>
     <t>335</t>
@@ -1932,13 +1926,13 @@
     <t>369</t>
   </si>
   <si>
-    <t>Soins intensifs spécialisés néonatalogique</t>
+    <t>Soins intensifs spécialisés néonatalogie</t>
   </si>
   <si>
     <t>370</t>
   </si>
   <si>
-    <t>Soins intensifs spécialisés pédiatrique</t>
+    <t>Soins intensifs spécialisés pédiatrie</t>
   </si>
   <si>
     <t>371</t>
@@ -3319,6 +3313,78 @@
   </si>
   <si>
     <t>Soins infirmiers en pratique avancée en santé mentale</t>
+  </si>
+  <si>
+    <t>618</t>
+  </si>
+  <si>
+    <t>Collecte de don de lait maternel cru</t>
+  </si>
+  <si>
+    <t>619</t>
+  </si>
+  <si>
+    <t>Distribution de lait maternel pasteurisé</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>Bilan psychomoteur</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>Soin psychomoteur</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>Education psychomotrice (pédagogie du développement psychomoteur)</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>Stimulation psychomotrice (stimulation du fonctionnement psychomoteur à visée préventive)</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>Rééducation de la graphomotricité et de l’écriture (dysgraphie)</t>
+  </si>
+  <si>
+    <t>625</t>
+  </si>
+  <si>
+    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
+  </si>
+  <si>
+    <t>626</t>
+  </si>
+  <si>
+    <t>Orthoptie orientation basse vision</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>Orthoptie orientation pédiatrique</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>Dispensation de médicaments et autres produits de santé appartenant au monopole pharmaceutique</t>
+  </si>
+  <si>
+    <t>629</t>
+  </si>
+  <si>
+    <t>Conseil et accompagnement dans la gestion des traitements</t>
   </si>
   <si>
     <t/>
@@ -3589,7 +3655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B551"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7905,15 +7971,103 @@
         <v>1102</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="s" s="2">
+        <v>1106</v>
+      </c>
+      <c r="B541" t="s" s="2">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="s" s="2">
+        <v>1108</v>
+      </c>
+      <c r="B542" t="s" s="2">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="s" s="2">
+        <v>1110</v>
+      </c>
+      <c r="B543" t="s" s="2">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="s" s="2">
+        <v>1112</v>
+      </c>
+      <c r="B544" t="s" s="2">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="s" s="2">
+        <v>1114</v>
+      </c>
+      <c r="B545" t="s" s="2">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="s" s="2">
+        <v>1116</v>
+      </c>
+      <c r="B546" t="s" s="2">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="s" s="2">
+        <v>1118</v>
+      </c>
+      <c r="B547" t="s" s="2">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="s" s="2">
+        <v>1120</v>
+      </c>
+      <c r="B548" t="s" s="2">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="s" s="2">
+        <v>1122</v>
+      </c>
+      <c r="B549" t="s" s="2">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="s" s="2">
+        <v>1124</v>
+      </c>
+      <c r="B550" t="s" s="2">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="s" s="2">
+        <v>1125</v>
+      </c>
+      <c r="B551" t="s" s="2">
+        <v>1126</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="1105">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -735,6 +735,12 @@
     <t>Urgences Médico-Psychologiques (CUMP)</t>
   </si>
   <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>Urgences spécialisées cardiologiques</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
@@ -1722,7 +1728,7 @@
     <t>334</t>
   </si>
   <si>
-    <t>Activité de dépistage et de prévention</t>
+    <t>Activité de prévention</t>
   </si>
   <si>
     <t>335</t>
@@ -1926,13 +1932,13 @@
     <t>369</t>
   </si>
   <si>
-    <t>Soins intensifs spécialisés néonatalogie</t>
+    <t>Soins intensifs spécialisés néonatalogique</t>
   </si>
   <si>
     <t>370</t>
   </si>
   <si>
-    <t>Soins intensifs spécialisés pédiatrie</t>
+    <t>Soins intensifs spécialisés pédiatrique</t>
   </si>
   <si>
     <t>371</t>
@@ -3313,78 +3319,6 @@
   </si>
   <si>
     <t>Soins infirmiers en pratique avancée en santé mentale</t>
-  </si>
-  <si>
-    <t>618</t>
-  </si>
-  <si>
-    <t>Collecte de don de lait maternel cru</t>
-  </si>
-  <si>
-    <t>619</t>
-  </si>
-  <si>
-    <t>Distribution de lait maternel pasteurisé</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>Bilan psychomoteur</t>
-  </si>
-  <si>
-    <t>621</t>
-  </si>
-  <si>
-    <t>Soin psychomoteur</t>
-  </si>
-  <si>
-    <t>622</t>
-  </si>
-  <si>
-    <t>Education psychomotrice (pédagogie du développement psychomoteur)</t>
-  </si>
-  <si>
-    <t>623</t>
-  </si>
-  <si>
-    <t>Stimulation psychomotrice (stimulation du fonctionnement psychomoteur à visée préventive)</t>
-  </si>
-  <si>
-    <t>624</t>
-  </si>
-  <si>
-    <t>Rééducation de la graphomotricité et de l’écriture (dysgraphie)</t>
-  </si>
-  <si>
-    <t>625</t>
-  </si>
-  <si>
-    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
-  </si>
-  <si>
-    <t>626</t>
-  </si>
-  <si>
-    <t>Orthoptie orientation basse vision</t>
-  </si>
-  <si>
-    <t>627</t>
-  </si>
-  <si>
-    <t>Orthoptie orientation pédiatrique</t>
-  </si>
-  <si>
-    <t>628</t>
-  </si>
-  <si>
-    <t>Dispensation de médicaments et autres produits de santé appartenant au monopole pharmaceutique</t>
-  </si>
-  <si>
-    <t>629</t>
-  </si>
-  <si>
-    <t>Conseil et accompagnement dans la gestion des traitements</t>
   </si>
   <si>
     <t/>
@@ -3655,7 +3589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B551"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7971,103 +7905,15 @@
         <v>1102</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
+        <v>1103</v>
+      </c>
+      <c r="B540" t="s" s="2">
         <v>1104</v>
-      </c>
-      <c r="B540" t="s" s="2">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="s" s="2">
-        <v>1106</v>
-      </c>
-      <c r="B541" t="s" s="2">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="s" s="2">
-        <v>1108</v>
-      </c>
-      <c r="B542" t="s" s="2">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="s" s="2">
-        <v>1110</v>
-      </c>
-      <c r="B543" t="s" s="2">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="s" s="2">
-        <v>1112</v>
-      </c>
-      <c r="B544" t="s" s="2">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="s" s="2">
-        <v>1114</v>
-      </c>
-      <c r="B545" t="s" s="2">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="s" s="2">
-        <v>1116</v>
-      </c>
-      <c r="B546" t="s" s="2">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="s" s="2">
-        <v>1118</v>
-      </c>
-      <c r="B547" t="s" s="2">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="s" s="2">
-        <v>1120</v>
-      </c>
-      <c r="B548" t="s" s="2">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="s" s="2">
-        <v>1122</v>
-      </c>
-      <c r="B549" t="s" s="2">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="s" s="2">
-        <v>1124</v>
-      </c>
-      <c r="B550" t="s" s="2">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="s" s="2">
-        <v>1125</v>
-      </c>
-      <c r="B551" t="s" s="2">
-        <v>1126</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="1131">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2178,7 +2178,7 @@
     <t>414</t>
   </si>
   <si>
-    <t>Soins de support en oncologie et hématologie</t>
+    <t>Soins de support</t>
   </si>
   <si>
     <t>416</t>
@@ -2382,7 +2382,7 @@
     <t>451</t>
   </si>
   <si>
-    <t>Exploration et prise en charge des troubles du sommeil</t>
+    <t>Exploration des troubles du sommeil</t>
   </si>
   <si>
     <t>452</t>
@@ -2496,7 +2496,7 @@
     <t>480</t>
   </si>
   <si>
-    <t>Médecine du sommeil</t>
+    <t>Médecine du sommeil (prise en charge des troubles du sommeil)</t>
   </si>
   <si>
     <t>481</t>
@@ -3385,6 +3385,18 @@
   </si>
   <si>
     <t>Conseil et accompagnement dans la gestion des traitements</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>Evaluation et accompagnement des auteurs de violences conjugales</t>
+  </si>
+  <si>
+    <t>631</t>
+  </si>
+  <si>
+    <t>Prise en charge et coordination de plaies et cicatrisations complexes</t>
   </si>
   <si>
     <t/>
@@ -3655,7 +3667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B551"/>
+  <dimension ref="A1:B553"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -8059,15 +8071,31 @@
         <v>1124</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="s" s="2">
+        <v>1128</v>
+      </c>
+      <c r="B552" t="s" s="2">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="s" s="2">
+        <v>1129</v>
+      </c>
+      <c r="B553" t="s" s="2">
+        <v>1130</v>
       </c>
     </row>
   </sheetData>
